--- a/data/trans_bre/Q45B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/Q45B_R-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,38</t>
+          <t>2,94; 6,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,83</t>
+          <t>0,4; 3,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,4</t>
+          <t>0,3; 3,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157,65; —</t>
+          <t>150,39; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,34; 432,95</t>
+          <t>12,16; 420,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 405,38</t>
+          <t>7,41; 381,05</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,9</t>
+          <t>4,98; 8,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,51</t>
+          <t>4,01; 7,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,28</t>
+          <t>1,84; 4,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196,34; 816,45</t>
+          <t>184,93; 796,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>181,64; 749,02</t>
+          <t>162,88; 753,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>142,99; 1392,03</t>
+          <t>139,75; 1233,82</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,1</t>
+          <t>1,81; 6,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,01</t>
+          <t>1,3; 6,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,91</t>
+          <t>1,25; 3,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64,83; 569,63</t>
+          <t>49,56; 514,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,59; 235,11</t>
+          <t>25,22; 237,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,36; 1936,87</t>
+          <t>83,84; 1935,07</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 9,14</t>
+          <t>4,27; 8,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,34</t>
+          <t>4,75; 8,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,21</t>
+          <t>1,44; 4,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100,25; 328,08</t>
+          <t>89,67; 317,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>108,15; 363,78</t>
+          <t>106,07; 348,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,81; 576,58</t>
+          <t>67,21; 587,26</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,87</t>
+          <t>4,74; 6,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,05</t>
+          <t>3,89; 5,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,26</t>
+          <t>1,91; 3,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196,86; 418,43</t>
+          <t>195,49; 412,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>127,3; 288,7</t>
+          <t>129,46; 283,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>150,8; 451,15</t>
+          <t>147,21; 454,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Q45B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/Q45B_R-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,26</t>
+          <t>2,95; 6,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,72</t>
+          <t>0,29; 3,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,41</t>
+          <t>0,34; 3,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150,39; —</t>
+          <t>182,34; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,16; 420,03</t>
+          <t>5,4; 416,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 381,05</t>
+          <t>7,89; 381,54</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,98</t>
+          <t>5,05; 8,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,72</t>
+          <t>3,97; 7,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,29</t>
+          <t>1,8; 4,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184,93; 796,8</t>
+          <t>199,79; 810,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>162,88; 753,95</t>
+          <t>159,58; 774,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>139,75; 1233,82</t>
+          <t>127,21; 1237,48</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,03</t>
+          <t>1,97; 6,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,22</t>
+          <t>1,36; 6,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,96</t>
+          <t>1,28; 3,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,56; 514,2</t>
+          <t>58,2; 498,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,22; 237,65</t>
+          <t>22,33; 235,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,84; 1935,07</t>
+          <t>79,14; 1960,6</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,8</t>
+          <t>4,45; 9,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,92</t>
+          <t>4,74; 8,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,23</t>
+          <t>1,51; 4,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,67; 317,94</t>
+          <t>92,66; 314,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>106,07; 348,48</t>
+          <t>92,78; 320,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,21; 587,26</t>
+          <t>81,79; 610,23</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,87</t>
+          <t>4,85; 6,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,93</t>
+          <t>3,9; 5,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,28</t>
+          <t>1,95; 3,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>195,49; 412,09</t>
+          <t>198,07; 411,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>129,46; 283,93</t>
+          <t>132,9; 280,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>147,21; 454,57</t>
+          <t>166,69; 459,51</t>
         </is>
       </c>
     </row>
